--- a/files/九龙-九龙塘-缇外.xlsx
+++ b/files/九龙-九龙塘-缇外.xlsx
@@ -8,11 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座 销控表" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -115,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -180,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -196,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -601,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -611,7 +474,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -706,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -752,7 +615,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -798,7 +661,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -844,7 +707,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -890,7 +753,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -936,7 +799,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1078,7 +941,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1124,7 +987,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1170,7 +1033,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1216,7 +1079,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1262,7 +1125,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1308,7 +1171,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1354,7 +1217,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1400,7 +1263,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1446,7 +1309,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1492,7 +1355,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1538,7 +1401,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1584,7 +1447,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1630,7 +1493,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1676,7 +1539,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1722,7 +1585,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1768,7 +1631,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1814,7 +1677,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1860,7 +1723,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1906,7 +1769,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1952,7 +1815,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -1998,7 +1861,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2044,7 +1907,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2090,7 +1953,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2136,7 +1999,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2282,7 +2145,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2328,7 +2191,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2374,7 +2237,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2420,7 +2283,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2616,7 +2479,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2662,7 +2525,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2758,7 +2621,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2854,7 +2717,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-23</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2900,7 +2763,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3188,7 +3051,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3234,7 +3097,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3280,7 +3143,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3326,7 +3189,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3422,7 +3285,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3468,7 +3331,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3524,6 +3387,144 @@
         <v>58651</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>院墅A</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>10692</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>1028000000</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>96147</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>院墅B</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>11589</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>86289</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>院墅C</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>11145</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>89726</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3536,1370 +3537,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>缇外 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>10 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>9 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>PH A</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>PH B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6&amp;7/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>PH A | 7912呎 (4+房)
-$60,000万
-$75,834/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>PH B | 8583呎 (4+房)
-$61,900万
-$72,119/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 4247呎 (4+房)
-$22,750万
-$53,567/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 4374呎 (4+房)
-$24,057万
-$55,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 4247呎 (4+房)
-$21,600万
-$50,859/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 4436呎 (4+房)
-$24,000万
-$54,103/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 4359呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 4432呎 (4+房)
-$21,500万
-$48,511/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 4269呎 (4+房)
-$21,000万
-$49,192/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 4071呎 (4+房)
-$17,200万
-$42,250/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr"/>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>缇外 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>PH | 8495呎 (4+房)
-$63,600万
-$74,868/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 4451呎 (4+房)
-$25,816万
-$58,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 4258呎 (4+房)
-$23,500万
-$55,190/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 4395呎 (4+房)
-$26,000万
-$59,158/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 4364呎 (4+房)
-$24,002万
-$55,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 4395呎 (4+房)
-$22,500万
-$51,195/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 4258呎 (4+房)
-$22,500万
-$52,842/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 4395呎 (4+房)
-$19,000万
-$43,231/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 4258呎 (4+房)
-$19,500万
-$45,796/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 4236呎 (4+房)
-$17,680万
-$41,737/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 4099呎 (4+房)
-$18,500万
-$45,133/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 4431呎 (4+房)
-$20,850万
-$47,055/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 3955呎 (4+房)
-$17,100万
-$43,236/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>缇外 - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>PH | 8402呎 (4+房)
-$60,000万
-$71,412/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 4378呎 (4+房)
-$25,000万
-$57,104/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 4394呎 (4+房)
-$25,000万
-$56,896/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 4378呎 (4+房)
-$25,580万
-$58,429/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 4557呎 (4+房)
-$24,500万
-$53,763/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 4378呎 (4+房)
-$23,000万
-$52,535/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 4394呎 (4+房)
-$22,000万
-$50,068/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 4378呎 (4+房)
-$19,200万
-$43,856/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 4394呎 (4+房)
-$19,200万
-$43,696/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 4324呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 4398呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 4072呎 (4+房)
-$18,000万
-$44,204/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 4311呎 (4+房)
-$20,850万
-$48,365/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>缇外 - 5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>PH | 8283呎 (4+房)
-$58,000万
-$70,023/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 4332呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 4378呎 (4+房)
-$25,000万
-$57,104/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 4437呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 4483呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 4274呎 (4+房)
-$23,000万
-$53,814/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 4378呎 (4+房)
-$23,000万
-$52,535/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 4274呎 (4+房)
-$19,180万
-$44,876/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 4483呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 4116呎 (4+房)
-$18,500万
-$44,947/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 4325呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 4194呎 (4+房)
-$18,500万
-$44,111/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 4074呎 (4+房)
-$18,000万
-$44,183/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>缇外 - 6座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>PH A</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>PH B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6&amp;7/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>PH A | 7403呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>PH B | 7915呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 3731呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 4262呎 (4+房)
-$24,500万
-$57,485/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 3701呎 (4+房)
-$19,000万
-$51,337/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 4261呎 (4+房)
-$22,500万
-$52,805/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 3728呎 (4+房)
-$19,200万
-$51,502/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 4260呎 (4+房)
-$21,500万
-$50,469/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 3723呎 (4+房)
-$18,000万
-$48,348/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 4359呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 3410呎 (4+房)
-$20,000万
-$58,651/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 3788呎 (4+房)
-$17,000万
-$44,879/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-九龙塘-缇外.xlsx
+++ b/files/九龙-九龙塘-缇外.xlsx
@@ -8,6 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +47,120 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +171,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -97,6 +251,72 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -474,7 +694,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -3537,4 +3757,1521 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>PH A</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>PH B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>6&amp;7</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>PH A | 7912呎 (4+房)
+$60000万
+$75,834/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>PH B | 8583呎 (4+房)
+$61900万
+$72,119/呎
+(24年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 4247呎 (4+房)
+$22750万
+$53,567/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 4374呎 (4+房)
+$24057万
+$55,000/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 4247呎 (4+房)
+$21600万
+$50,859/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 4436呎 (4+房)
+$24000万
+$54,103/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 4359呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 4432呎 (4+房)
+$21500万
+$48,511/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 4269呎 (4+房)
+$21000万
+$49,192/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 4071呎 (4+房)
+$17200万
+$42,250/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>PH | 8495呎 (4+房)
+$63600万
+$74,868/呎
+(24年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 4451呎 (4+房)
+$25816万
+$58,000/呎
+(22年-11月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 4258呎 (4+房)
+$23500万
+$55,190/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 4395呎 (4+房)
+$26000万
+$59,158/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 4364呎 (4+房)
+$24002万
+$55,000/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 4395呎 (4+房)
+$22500万
+$51,195/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 4258呎 (4+房)
+$22500万
+$52,842/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 4395呎 (4+房)
+$19000万
+$43,231/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 4258呎 (4+房)
+$19500万
+$45,796/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 4236呎 (4+房)
+$17680万
+$41,737/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 4099呎 (4+房)
+$18500万
+$45,133/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 4431呎 (4+房)
+$20850万
+$47,055/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 3955呎 (4+房)
+$17100万
+$43,236/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>PH | 8402呎 (4+房)
+$60000万
+$71,412/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 4378呎 (4+房)
+$25000万
+$57,104/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 4394呎 (4+房)
+$25000万
+$56,896/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 4378呎 (4+房)
+$25580万
+$58,429/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 4557呎 (4+房)
+$24500万
+$53,763/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 4378呎 (4+房)
+$23000万
+$52,535/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 4394呎 (4+房)
+$22000万
+$50,068/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 4378呎 (4+房)
+$19200万
+$43,856/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 4394呎 (4+房)
+$19200万
+$43,696/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 4324呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 4398呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 4072呎 (4+房)
+$18000万
+$44,204/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 4311呎 (4+房)
+$20850万
+$48,365/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>PH | 8283呎 (4+房)
+$58000万
+$70,023/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 4332呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 4378呎 (4+房)
+$25000万
+$57,104/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 4437呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 4483呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 4274呎 (4+房)
+$23000万
+$53,814/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 4378呎 (4+房)
+$23000万
+$52,535/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 4274呎 (4+房)
+$19180万
+$44,876/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 4483呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 4116呎 (4+房)
+$18500万
+$44,947/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 4325呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 4194呎 (4+房)
+$18500万
+$44,111/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 4074呎 (4+房)
+$18000万
+$44,183/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>PH A</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>PH B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>6&amp;7</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>PH A | 7403呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>PH B | 7915呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 3731呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 4262呎 (4+房)
+$24500万
+$57,485/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 3701呎 (4+房)
+$19000万
+$51,337/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 4261呎 (4+房)
+$22500万
+$52,805/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 3728呎 (4+房)
+$19200万
+$51,502/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 4260呎 (4+房)
+$21500万
+$50,469/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 3723呎 (4+房)
+$18000万
+$48,348/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 4359呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 3410呎 (4+房)
+$20000万
+$58,651/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 3788呎 (4+房)
+$17000万
+$44,879/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>缇外 - 独立屋销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>3 套</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>3 套</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>院墅A</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>院墅B</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>院墅C</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>独立屋</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>院墅A
+10692呎 (4+房)
+(24年-08月)
+$10.28亿
+$96,147/呎</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>院墅B
+11589呎 (4+房)
+(24年-04月)
+$10.00亿
+$86,289/呎</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>院墅C
+11145呎 (4+房)
+(25年-05月)
+$10.00亿
+$89,726/呎</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-九龙塘-缇外.xlsx
+++ b/files/九龙-九龙塘-缇外.xlsx
@@ -694,7 +694,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-九龙塘-缇外.xlsx
+++ b/files/九龙-九龙塘-缇外.xlsx
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -697,6 +697,10 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -754,6 +758,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -800,6 +824,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -846,6 +890,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -892,6 +956,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -938,6 +1022,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -984,6 +1088,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1030,6 +1154,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1076,6 +1220,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1126,6 +1290,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1172,6 +1356,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1218,6 +1422,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1264,6 +1488,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1310,6 +1554,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1356,6 +1620,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1402,6 +1686,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1448,6 +1752,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1494,6 +1818,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1540,6 +1884,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1586,6 +1950,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1632,6 +2016,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1678,6 +2082,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1724,6 +2148,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1770,6 +2214,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1816,6 +2280,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1862,6 +2346,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1908,6 +2412,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1954,6 +2478,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2000,6 +2544,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2046,6 +2610,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2092,6 +2676,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2138,6 +2742,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2184,6 +2808,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2230,6 +2874,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2280,6 +2944,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2330,6 +3014,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2376,6 +3080,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2422,6 +3146,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2468,6 +3212,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2514,6 +3278,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2564,6 +3348,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2614,6 +3418,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2664,6 +3488,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2710,6 +3554,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2756,6 +3620,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2806,6 +3690,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2852,6 +3756,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2902,6 +3826,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2948,6 +3892,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2994,6 +3958,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3040,6 +4024,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3090,6 +4094,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3140,6 +4164,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3186,6 +4230,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3236,6 +4300,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3282,6 +4366,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3328,6 +4432,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3374,6 +4498,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3420,6 +4564,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3470,6 +4634,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3516,6 +4700,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3562,6 +4766,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3608,6 +4832,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3654,6 +4898,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3700,6 +4964,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3746,13 +5030,33 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -3886,7 +5190,7 @@
           <t>PH A | 7912呎 (4+房)
 $60000万
 $75,834/呎
-(24年-05月)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -3894,7 +5198,7 @@
           <t>PH B | 8583呎 (4+房)
 $61900万
 $72,119/呎
-(24年-02月)</t>
+(24年-02月-08日)</t>
         </is>
       </c>
     </row>
@@ -3909,7 +5213,7 @@
           <t>A | 4247呎 (4+房)
 $22750万
 $53,567/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -3917,7 +5221,7 @@
           <t>B | 4374呎 (4+房)
 $24057万
 $55,000/呎
-(22年-10月)</t>
+(22年-10月-31日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -3934,7 +5238,7 @@
           <t>A | 4247呎 (4+房)
 $21600万
 $50,859/呎
-(24年-06月)</t>
+(24年-06月-19日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -3942,7 +5246,7 @@
           <t>B | 4436呎 (4+房)
 $24000万
 $54,103/呎
-(24年-01月)</t>
+(24年-01月-11日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -3967,7 +5271,7 @@
           <t>B | 4432呎 (4+房)
 $21500万
 $48,511/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -3984,7 +5288,7 @@
           <t>A | 4269呎 (4+房)
 $21000万
 $49,192/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -4002,7 +5306,7 @@
           <t>A | 4071呎 (4+房)
 $17200万
 $42,250/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
@@ -4139,7 +5443,7 @@
           <t>PH | 8495呎 (4+房)
 $63600万
 $74,868/呎
-(24年-02月)</t>
+(24年-02月-21日)</t>
         </is>
       </c>
     </row>
@@ -4154,7 +5458,7 @@
           <t>A | 4451呎 (4+房)
 $25816万
 $58,000/呎
-(22年-11月)</t>
+(22年-11月-15日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -4162,7 +5466,7 @@
           <t>B | 4258呎 (4+房)
 $23500万
 $55,190/呎
-(24年-03月)</t>
+(24年-03月-11日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -4178,7 +5482,7 @@
           <t>A | 4395呎 (4+房)
 $26000万
 $59,158/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -4186,7 +5490,7 @@
           <t>B | 4364呎 (4+房)
 $24002万
 $55,000/呎
-(23年-08月)</t>
+(23年-08月-28日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -4202,7 +5506,7 @@
           <t>A | 4395呎 (4+房)
 $22500万
 $51,195/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -4210,7 +5514,7 @@
           <t>B | 4258呎 (4+房)
 $22500万
 $52,842/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -4226,7 +5530,7 @@
           <t>A | 4395呎 (4+房)
 $19000万
 $43,231/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -4234,7 +5538,7 @@
           <t>B | 4258呎 (4+房)
 $19500万
 $45,796/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -4250,7 +5554,7 @@
           <t>A | 4236呎 (4+房)
 $17680万
 $41,737/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -4258,7 +5562,7 @@
           <t>B | 4099呎 (4+房)
 $18500万
 $45,133/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -4274,7 +5578,7 @@
           <t>A | 4431呎 (4+房)
 $20850万
 $47,055/呎
-(24年-01月)</t>
+(24年-01月-18日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -4282,7 +5586,7 @@
           <t>B | 3955呎 (4+房)
 $17100万
 $43,236/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -4417,7 +5721,7 @@
           <t>PH | 8402呎 (4+房)
 $60000万
 $71,412/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
     </row>
@@ -4432,7 +5736,7 @@
           <t>A | 4378呎 (4+房)
 $25000万
 $57,104/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -4440,7 +5744,7 @@
           <t>B | 4394呎 (4+房)
 $25000万
 $56,896/呎
-(24年-07月)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -4456,7 +5760,7 @@
           <t>A | 4378呎 (4+房)
 $25580万
 $58,429/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -4464,7 +5768,7 @@
           <t>B | 4557呎 (4+房)
 $24500万
 $53,763/呎
-(23年-12月)</t>
+(23年-12月-21日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -4480,7 +5784,7 @@
           <t>A | 4378呎 (4+房)
 $23000万
 $52,535/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -4488,7 +5792,7 @@
           <t>B | 4394呎 (4+房)
 $22000万
 $50,068/呎
-(24年-09月)</t>
+(24年-09月-15日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -4504,7 +5808,7 @@
           <t>A | 4378呎 (4+房)
 $19200万
 $43,856/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -4512,7 +5816,7 @@
           <t>B | 4394呎 (4+房)
 $19200万
 $43,696/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -4552,7 +5856,7 @@
           <t>A | 4072呎 (4+房)
 $18000万
 $44,204/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -4560,7 +5864,7 @@
           <t>B | 4311呎 (4+房)
 $20850万
 $48,365/呎
-(24年-09月)</t>
+(24年-09月-29日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -4695,7 +5999,7 @@
           <t>PH | 8283呎 (4+房)
 $58000万
 $70,023/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -4718,7 +6022,7 @@
           <t>B | 4378呎 (4+房)
 $25000万
 $57,104/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -4758,7 +6062,7 @@
           <t>A | 4274呎 (4+房)
 $23000万
 $53,814/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -4766,7 +6070,7 @@
           <t>B | 4378呎 (4+房)
 $23000万
 $52,535/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -4782,7 +6086,7 @@
           <t>A | 4274呎 (4+房)
 $19180万
 $44,876/呎
-(24年-10月)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -4806,7 +6110,7 @@
           <t>A | 4116呎 (4+房)
 $18500万
 $44,947/呎
-(25年-02月)</t>
+(25年-02月-23日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -4830,7 +6134,7 @@
           <t>A | 4194呎 (4+房)
 $18500万
 $44,111/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -4838,7 +6142,7 @@
           <t>B | 4074呎 (4+房)
 $18000万
 $44,183/呎
-(24年-07月)</t>
+(24年-07月-22日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -5010,7 +6314,7 @@
           <t>B | 4262呎 (4+房)
 $24500万
 $57,485/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -5027,7 +6331,7 @@
           <t>A | 3701呎 (4+房)
 $19000万
 $51,337/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -5035,7 +6339,7 @@
           <t>B | 4261呎 (4+房)
 $22500万
 $52,805/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5052,7 +6356,7 @@
           <t>A | 3728呎 (4+房)
 $19200万
 $51,502/呎
-(24年-07月)</t>
+(24年-07月-24日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -5060,7 +6364,7 @@
           <t>B | 4260呎 (4+房)
 $21500万
 $50,469/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -5077,7 +6381,7 @@
           <t>A | 3723呎 (4+房)
 $18000万
 $48,348/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -5102,7 +6406,7 @@
           <t>A | 3410呎 (4+房)
 $20000万
 $58,651/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -5110,7 +6414,7 @@
           <t>B | 3788呎 (4+房)
 $17000万
 $44,879/呎
-(25年-09月)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -5243,7 +6547,7 @@
         <is>
           <t>院墅A
 10692呎 (4+房)
-(24年-08月)
+(24年-08月-27日)
 $10.28亿
 $96,147/呎</t>
         </is>
@@ -5252,7 +6556,7 @@
         <is>
           <t>院墅B
 11589呎 (4+房)
-(24年-04月)
+(24年-04月-23日)
 $10.00亿
 $86,289/呎</t>
         </is>
@@ -5261,7 +6565,7 @@
         <is>
           <t>院墅C
 11145呎 (4+房)
-(25年-05月)
+(25年-05月-26日)
 $10.00亿
 $89,726/呎</t>
         </is>

--- a/files/九龙-九龙塘-缇外.xlsx
+++ b/files/九龙-九龙塘-缇外.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,6 +122,12 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -236,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -301,22 +307,25 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1270,7 +1279,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1280,12 +1289,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1295,12 +1304,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1310,7 +1319,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5126,27 +5135,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
@@ -5261,9 +5270,9 @@
       <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 4359呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -5827,7 +5836,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 4324呎 (4+房)
 -
@@ -5835,7 +5844,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 4398呎 (4+房)
 -
@@ -6009,7 +6018,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 4332呎 (4+房)
 -
@@ -6033,7 +6042,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 4437呎 (4+房)
 -
@@ -6041,7 +6050,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 4483呎 (4+房)
 -
@@ -6089,7 +6098,7 @@
 (24年-10月-09日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 4483呎 (4+房)
 -
@@ -6113,7 +6122,7 @@
 (25年-02月-23日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 4325呎 (4+房)
 -
@@ -6278,7 +6287,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>PH A | 7403呎 (4+房)
 -
@@ -6286,7 +6295,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>PH B | 7915呎 (4+房)
 -
@@ -6301,7 +6310,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 3731呎 (4+房)
 -
@@ -6384,7 +6393,7 @@
 (24年-11月-28日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 4359呎 (4+房)
 -
@@ -6484,32 +6493,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="25" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>

--- a/files/九龙-九龙塘-缇外.xlsx
+++ b/files/九龙-九龙塘-缇外.xlsx
@@ -5199,7 +5199,7 @@
           <t>PH A | 7912呎 (4+房)
 $60000万
 $75,834/呎
-(24年-05月-08日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -5207,7 +5207,7 @@
           <t>PH B | 8583呎 (4+房)
 $61900万
 $72,119/呎
-(24年-02月-08日)</t>
+(24年-02月)</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
           <t>A | 4247呎 (4+房)
 $22750万
 $53,567/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -5230,7 +5230,7 @@
           <t>B | 4374呎 (4+房)
 $24057万
 $55,000/呎
-(22年-10月-31日)</t>
+(22年-10月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
           <t>A | 4247呎 (4+房)
 $21600万
 $50,859/呎
-(24年-06月-19日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -5255,7 +5255,7 @@
           <t>B | 4436呎 (4+房)
 $24000万
 $54,103/呎
-(24年-01月-11日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5280,7 +5280,7 @@
           <t>B | 4432呎 (4+房)
 $21500万
 $48,511/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -5297,7 +5297,7 @@
           <t>A | 4269呎 (4+房)
 $21000万
 $49,192/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -5315,7 +5315,7 @@
           <t>A | 4071呎 (4+房)
 $17200万
 $42,250/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
@@ -5452,7 +5452,7 @@
           <t>PH | 8495呎 (4+房)
 $63600万
 $74,868/呎
-(24年-02月-21日)</t>
+(24年-02月)</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
           <t>A | 4451呎 (4+房)
 $25816万
 $58,000/呎
-(22年-11月-15日)</t>
+(22年-11月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -5475,7 +5475,7 @@
           <t>B | 4258呎 (4+房)
 $23500万
 $55,190/呎
-(24年-03月-11日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -5491,7 +5491,7 @@
           <t>A | 4395呎 (4+房)
 $26000万
 $59,158/呎
-(24年-10月-06日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -5499,7 +5499,7 @@
           <t>B | 4364呎 (4+房)
 $24002万
 $55,000/呎
-(23年-08月-28日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5515,7 +5515,7 @@
           <t>A | 4395呎 (4+房)
 $22500万
 $51,195/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -5523,7 +5523,7 @@
           <t>B | 4258呎 (4+房)
 $22500万
 $52,842/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -5539,7 +5539,7 @@
           <t>A | 4395呎 (4+房)
 $19000万
 $43,231/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -5547,7 +5547,7 @@
           <t>B | 4258呎 (4+房)
 $19500万
 $45,796/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -5563,7 +5563,7 @@
           <t>A | 4236呎 (4+房)
 $17680万
 $41,737/呎
-(26年-01月-28日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -5571,7 +5571,7 @@
           <t>B | 4099呎 (4+房)
 $18500万
 $45,133/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -5587,7 +5587,7 @@
           <t>A | 4431呎 (4+房)
 $20850万
 $47,055/呎
-(24年-01月-18日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -5595,7 +5595,7 @@
           <t>B | 3955呎 (4+房)
 $17100万
 $43,236/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -5730,7 +5730,7 @@
           <t>PH | 8402呎 (4+房)
 $60000万
 $71,412/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
           <t>A | 4378呎 (4+房)
 $25000万
 $57,104/呎
-(24年-07月-01日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -5753,7 +5753,7 @@
           <t>B | 4394呎 (4+房)
 $25000万
 $56,896/呎
-(24年-07月-18日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -5769,7 +5769,7 @@
           <t>A | 4378呎 (4+房)
 $25580万
 $58,429/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -5777,7 +5777,7 @@
           <t>B | 4557呎 (4+房)
 $24500万
 $53,763/呎
-(23年-12月-21日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5793,7 +5793,7 @@
           <t>A | 4378呎 (4+房)
 $23000万
 $52,535/呎
-(24年-08月-07日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -5801,7 +5801,7 @@
           <t>B | 4394呎 (4+房)
 $22000万
 $50,068/呎
-(24年-09月-15日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -5817,7 +5817,7 @@
           <t>A | 4378呎 (4+房)
 $19200万
 $43,856/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -5825,7 +5825,7 @@
           <t>B | 4394呎 (4+房)
 $19200万
 $43,696/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -5865,7 +5865,7 @@
           <t>A | 4072呎 (4+房)
 $18000万
 $44,204/呎
-(24年-08月-05日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -5873,7 +5873,7 @@
           <t>B | 4311呎 (4+房)
 $20850万
 $48,365/呎
-(24年-09月-29日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -6008,7 +6008,7 @@
           <t>PH | 8283呎 (4+房)
 $58000万
 $70,023/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
           <t>B | 4378呎 (4+房)
 $25000万
 $57,104/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -6071,7 +6071,7 @@
           <t>A | 4274呎 (4+房)
 $23000万
 $53,814/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -6079,7 +6079,7 @@
           <t>B | 4378呎 (4+房)
 $23000万
 $52,535/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -6095,7 +6095,7 @@
           <t>A | 4274呎 (4+房)
 $19180万
 $44,876/呎
-(24年-10月-09日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -6119,7 +6119,7 @@
           <t>A | 4116呎 (4+房)
 $18500万
 $44,947/呎
-(25年-02月-23日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -6143,7 +6143,7 @@
           <t>A | 4194呎 (4+房)
 $18500万
 $44,111/呎
-(24年-10月-20日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -6151,7 +6151,7 @@
           <t>B | 4074呎 (4+房)
 $18000万
 $44,183/呎
-(24年-07月-22日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -6323,7 +6323,7 @@
           <t>B | 4262呎 (4+房)
 $24500万
 $57,485/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -6340,7 +6340,7 @@
           <t>A | 3701呎 (4+房)
 $19000万
 $51,337/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -6348,7 +6348,7 @@
           <t>B | 4261呎 (4+房)
 $22500万
 $52,805/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -6365,7 +6365,7 @@
           <t>A | 3728呎 (4+房)
 $19200万
 $51,502/呎
-(24年-07月-24日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -6373,7 +6373,7 @@
           <t>B | 4260呎 (4+房)
 $21500万
 $50,469/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -6390,7 +6390,7 @@
           <t>A | 3723呎 (4+房)
 $18000万
 $48,348/呎
-(24年-11月-28日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -6415,7 +6415,7 @@
           <t>A | 3410呎 (4+房)
 $20000万
 $58,651/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -6423,7 +6423,7 @@
           <t>B | 3788呎 (4+房)
 $17000万
 $44,879/呎
-(25年-09月-02日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -6556,7 +6556,7 @@
         <is>
           <t>院墅A
 10692呎 (4+房)
-(24年-08月-27日)
+(24年-08月)
 $10.28亿
 $96,147/呎</t>
         </is>
@@ -6565,7 +6565,7 @@
         <is>
           <t>院墅B
 11589呎 (4+房)
-(24年-04月-23日)
+(24年-04月)
 $10.00亿
 $86,289/呎</t>
         </is>
@@ -6574,7 +6574,7 @@
         <is>
           <t>院墅C
 11145呎 (4+房)
-(25年-05月-26日)
+(25年-05月)
 $10.00亿
 $89,726/呎</t>
         </is>

--- a/files/九龙-九龙塘-缇外.xlsx
+++ b/files/九龙-九龙塘-缇外.xlsx
@@ -5199,7 +5199,7 @@
           <t>PH A | 7912呎 (4+房)
 $60000万
 $75,834/呎
-(24年-05月)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -5207,7 +5207,7 @@
           <t>PH B | 8583呎 (4+房)
 $61900万
 $72,119/呎
-(24年-02月)</t>
+(24年-02月-08日)</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
           <t>A | 4247呎 (4+房)
 $22750万
 $53,567/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -5230,7 +5230,7 @@
           <t>B | 4374呎 (4+房)
 $24057万
 $55,000/呎
-(22年-10月)</t>
+(22年-10月-31日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
           <t>A | 4247呎 (4+房)
 $21600万
 $50,859/呎
-(24年-06月)</t>
+(24年-06月-19日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -5255,7 +5255,7 @@
           <t>B | 4436呎 (4+房)
 $24000万
 $54,103/呎
-(24年-01月)</t>
+(24年-01月-11日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5280,7 +5280,7 @@
           <t>B | 4432呎 (4+房)
 $21500万
 $48,511/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -5297,7 +5297,7 @@
           <t>A | 4269呎 (4+房)
 $21000万
 $49,192/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -5315,7 +5315,7 @@
           <t>A | 4071呎 (4+房)
 $17200万
 $42,250/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
@@ -5452,7 +5452,7 @@
           <t>PH | 8495呎 (4+房)
 $63600万
 $74,868/呎
-(24年-02月)</t>
+(24年-02月-21日)</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
           <t>A | 4451呎 (4+房)
 $25816万
 $58,000/呎
-(22年-11月)</t>
+(22年-11月-15日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -5475,7 +5475,7 @@
           <t>B | 4258呎 (4+房)
 $23500万
 $55,190/呎
-(24年-03月)</t>
+(24年-03月-11日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -5491,7 +5491,7 @@
           <t>A | 4395呎 (4+房)
 $26000万
 $59,158/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -5499,7 +5499,7 @@
           <t>B | 4364呎 (4+房)
 $24002万
 $55,000/呎
-(23年-08月)</t>
+(23年-08月-28日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5515,7 +5515,7 @@
           <t>A | 4395呎 (4+房)
 $22500万
 $51,195/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -5523,7 +5523,7 @@
           <t>B | 4258呎 (4+房)
 $22500万
 $52,842/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -5539,7 +5539,7 @@
           <t>A | 4395呎 (4+房)
 $19000万
 $43,231/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -5547,7 +5547,7 @@
           <t>B | 4258呎 (4+房)
 $19500万
 $45,796/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -5563,7 +5563,7 @@
           <t>A | 4236呎 (4+房)
 $17680万
 $41,737/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -5571,7 +5571,7 @@
           <t>B | 4099呎 (4+房)
 $18500万
 $45,133/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -5587,7 +5587,7 @@
           <t>A | 4431呎 (4+房)
 $20850万
 $47,055/呎
-(24年-01月)</t>
+(24年-01月-18日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -5595,7 +5595,7 @@
           <t>B | 3955呎 (4+房)
 $17100万
 $43,236/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -5730,7 +5730,7 @@
           <t>PH | 8402呎 (4+房)
 $60000万
 $71,412/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
           <t>A | 4378呎 (4+房)
 $25000万
 $57,104/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -5753,7 +5753,7 @@
           <t>B | 4394呎 (4+房)
 $25000万
 $56,896/呎
-(24年-07月)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -5769,7 +5769,7 @@
           <t>A | 4378呎 (4+房)
 $25580万
 $58,429/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -5777,7 +5777,7 @@
           <t>B | 4557呎 (4+房)
 $24500万
 $53,763/呎
-(23年-12月)</t>
+(23年-12月-21日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5793,7 +5793,7 @@
           <t>A | 4378呎 (4+房)
 $23000万
 $52,535/呎
-(24年-08月)</t>
+(24年-08月-07日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -5801,7 +5801,7 @@
           <t>B | 4394呎 (4+房)
 $22000万
 $50,068/呎
-(24年-09月)</t>
+(24年-09月-15日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -5817,7 +5817,7 @@
           <t>A | 4378呎 (4+房)
 $19200万
 $43,856/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -5825,7 +5825,7 @@
           <t>B | 4394呎 (4+房)
 $19200万
 $43,696/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -5865,7 +5865,7 @@
           <t>A | 4072呎 (4+房)
 $18000万
 $44,204/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -5873,7 +5873,7 @@
           <t>B | 4311呎 (4+房)
 $20850万
 $48,365/呎
-(24年-09月)</t>
+(24年-09月-29日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -6008,7 +6008,7 @@
           <t>PH | 8283呎 (4+房)
 $58000万
 $70,023/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
           <t>B | 4378呎 (4+房)
 $25000万
 $57,104/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -6071,7 +6071,7 @@
           <t>A | 4274呎 (4+房)
 $23000万
 $53,814/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -6079,7 +6079,7 @@
           <t>B | 4378呎 (4+房)
 $23000万
 $52,535/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -6095,7 +6095,7 @@
           <t>A | 4274呎 (4+房)
 $19180万
 $44,876/呎
-(24年-10月)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -6119,7 +6119,7 @@
           <t>A | 4116呎 (4+房)
 $18500万
 $44,947/呎
-(25年-02月)</t>
+(25年-02月-23日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -6143,7 +6143,7 @@
           <t>A | 4194呎 (4+房)
 $18500万
 $44,111/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -6151,7 +6151,7 @@
           <t>B | 4074呎 (4+房)
 $18000万
 $44,183/呎
-(24年-07月)</t>
+(24年-07月-22日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -6323,7 +6323,7 @@
           <t>B | 4262呎 (4+房)
 $24500万
 $57,485/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -6340,7 +6340,7 @@
           <t>A | 3701呎 (4+房)
 $19000万
 $51,337/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -6348,7 +6348,7 @@
           <t>B | 4261呎 (4+房)
 $22500万
 $52,805/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -6365,7 +6365,7 @@
           <t>A | 3728呎 (4+房)
 $19200万
 $51,502/呎
-(24年-07月)</t>
+(24年-07月-24日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -6373,7 +6373,7 @@
           <t>B | 4260呎 (4+房)
 $21500万
 $50,469/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -6390,7 +6390,7 @@
           <t>A | 3723呎 (4+房)
 $18000万
 $48,348/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -6415,7 +6415,7 @@
           <t>A | 3410呎 (4+房)
 $20000万
 $58,651/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -6423,7 +6423,7 @@
           <t>B | 3788呎 (4+房)
 $17000万
 $44,879/呎
-(25年-09月)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -6556,7 +6556,7 @@
         <is>
           <t>院墅A
 10692呎 (4+房)
-(24年-08月)
+(24年-08月-27日)
 $10.28亿
 $96,147/呎</t>
         </is>
@@ -6565,7 +6565,7 @@
         <is>
           <t>院墅B
 11589呎 (4+房)
-(24年-04月)
+(24年-04月-23日)
 $10.00亿
 $86,289/呎</t>
         </is>
@@ -6574,7 +6574,7 @@
         <is>
           <t>院墅C
 11145呎 (4+房)
-(25年-05月)
+(25年-05月-26日)
 $10.00亿
 $89,726/呎</t>
         </is>
